--- a/Selecciones_2026.xlsx
+++ b/Selecciones_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e68a3986c888dc4/Desktop/Artefactos/GOLF/Temporada 2027/Distinguidos_PGATour/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_DD14C3ABB9E48FA76046DBDE7895F7F410C0F599" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D3BF7DD-045B-40C6-938B-D09E58FA15D2}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_DD14C3ABB9E48FA76046DBDE7895F7F410C0F599" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EFB9FDA-5D8F-41D9-A1C3-5468AE2C21AD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="174">
   <si>
     <t>Planilla de selecciones – Distinguidos PGA Tour</t>
   </si>
@@ -544,6 +544,15 @@
   </si>
   <si>
     <t>Cameron Tankersley</t>
+  </si>
+  <si>
+    <t>Adam Hadwin</t>
+  </si>
+  <si>
+    <t>David Lipsky</t>
+  </si>
+  <si>
+    <t>Andrew Novak</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3874,6 +3883,86 @@
         <v>170</v>
       </c>
     </row>
+    <row r="118" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A118" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B118" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" t="s">
+        <v>171</v>
+      </c>
+      <c r="D118" t="s">
+        <v>173</v>
+      </c>
+      <c r="E118" t="s">
+        <v>171</v>
+      </c>
+      <c r="F118" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A119" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="s">
+        <v>114</v>
+      </c>
+      <c r="D119" t="s">
+        <v>169</v>
+      </c>
+      <c r="E119" t="s">
+        <v>114</v>
+      </c>
+      <c r="F119" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A120" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" t="s">
+        <v>126</v>
+      </c>
+      <c r="D120" t="s">
+        <v>170</v>
+      </c>
+      <c r="E120" t="s">
+        <v>126</v>
+      </c>
+      <c r="F120" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A121" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B121" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" t="s">
+        <v>172</v>
+      </c>
+      <c r="D121" t="s">
+        <v>171</v>
+      </c>
+      <c r="E121" t="s">
+        <v>172</v>
+      </c>
+      <c r="F121" t="s">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -3883,7 +3972,7 @@
           <x14:formula1>
             <xm:f>Torneos!$A$2:$A$80</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A116 A118:A500</xm:sqref>
+          <xm:sqref>A2:A116 A122:A500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0300-000001000000}">
           <x14:formula1>

--- a/Selecciones_2026.xlsx
+++ b/Selecciones_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3" documentId="11_DD14C3ABB9E48FA76046DBDE7895F7F410C0F599" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EFB9FDA-5D8F-41D9-A1C3-5468AE2C21AD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>

--- a/Selecciones_2026.xlsx
+++ b/Selecciones_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e68a3986c888dc4/Desktop/Artefactos/GOLF/Temporada 2027/Distinguidos_PGATour/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infog\Desktop\Golf 2027\Distinguidos_PGATour\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_DD14C3ABB9E48FA76046DBDE7895F7F410C0F599" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EFB9FDA-5D8F-41D9-A1C3-5468AE2C21AD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E77996-86CE-4EF2-B520-E44825FA5B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="165">
   <si>
     <t>Planilla de selecciones – Distinguidos PGA Tour</t>
   </si>
@@ -213,9 +213,6 @@
     <t>Genesis Scottish</t>
   </si>
   <si>
-    <t>Sí</t>
-  </si>
-  <si>
     <t>Jugador 1</t>
   </si>
   <si>
@@ -529,37 +526,13 @@
   </si>
   <si>
     <t>Puntos que reciben el 1°, 2° y 3° de la polla en cada torneo. Fuente: hoja Tabla Gral. de tu Excel.</t>
-  </si>
-  <si>
-    <t>VidantaWorld Mexico Open</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
-    <t>Austin Eckroat</t>
-  </si>
-  <si>
-    <t>Christo Lamprecht</t>
-  </si>
-  <si>
-    <t>Cameron Tankersley</t>
-  </si>
-  <si>
-    <t>Adam Hadwin</t>
-  </si>
-  <si>
-    <t>David Lipsky</t>
-  </si>
-  <si>
-    <t>Andrew Novak</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,13 +583,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -626,12 +594,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F7A4D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -647,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -662,12 +624,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1212,7 +1171,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="9"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="4" t="s">
         <v>31</v>
       </c>
@@ -1226,7 +1185,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="9"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="4" t="s">
         <v>36</v>
       </c>
@@ -1240,7 +1199,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="9"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="4" t="s">
         <v>36</v>
       </c>
@@ -1254,7 +1213,7 @@
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="9"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="4" t="s">
         <v>36</v>
       </c>
@@ -1268,7 +1227,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="9"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="4" t="s">
         <v>36</v>
       </c>
@@ -1282,7 +1241,7 @@
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="4" t="s">
         <v>42</v>
       </c>
@@ -1296,7 +1255,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="9"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="4" t="s">
         <v>42</v>
       </c>
@@ -1310,7 +1269,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="9"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="4" t="s">
         <v>42</v>
       </c>
@@ -1324,7 +1283,7 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="9"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="4" t="s">
         <v>47</v>
       </c>
@@ -1338,7 +1297,7 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="9"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="4" t="s">
         <v>47</v>
       </c>
@@ -1352,7 +1311,7 @@
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="4" t="s">
         <v>47</v>
       </c>
@@ -1366,7 +1325,7 @@
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="9"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="4" t="s">
         <v>47</v>
       </c>
@@ -1380,7 +1339,7 @@
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="4" t="s">
         <v>47</v>
       </c>
@@ -1394,7 +1353,7 @@
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="4" t="s">
         <v>53</v>
       </c>
@@ -1408,7 +1367,7 @@
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="9"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="4" t="s">
         <v>53</v>
       </c>
@@ -1422,7 +1381,7 @@
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="9"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="4" t="s">
         <v>53</v>
       </c>
@@ -1434,9 +1393,9 @@
       <c r="B24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="4"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="9"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="4" t="s">
         <v>53</v>
       </c>
@@ -1450,7 +1409,7 @@
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="9"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="4" t="s">
         <v>58</v>
       </c>
@@ -1464,51 +1423,39 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="9"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="8">
-        <v>46324</v>
-      </c>
-      <c r="D27" s="8">
-        <v>46327</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>167</v>
-      </c>
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E28" s="10"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E29" s="10"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E30" s="10"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E31" s="10"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E32" s="10"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" spans="5:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E33" s="10"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" spans="5:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E34" s="10"/>
+      <c r="E34" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1551,16 +1498,16 @@
         <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1571,16 +1518,16 @@
         <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1591,16 +1538,16 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1611,16 +1558,16 @@
         <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1631,16 +1578,16 @@
         <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1651,16 +1598,16 @@
         <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1671,16 +1618,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1691,16 +1638,16 @@
         <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1711,16 +1658,16 @@
         <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1731,16 +1678,16 @@
         <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1751,16 +1698,16 @@
         <v>17</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1771,16 +1718,16 @@
         <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1791,16 +1738,16 @@
         <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1811,16 +1758,16 @@
         <v>15</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1831,16 +1778,16 @@
         <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1851,16 +1798,16 @@
         <v>17</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1871,16 +1818,16 @@
         <v>13</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1891,16 +1838,16 @@
         <v>14</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1911,16 +1858,16 @@
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1931,16 +1878,16 @@
         <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1951,16 +1898,16 @@
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1971,16 +1918,16 @@
         <v>13</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1991,16 +1938,16 @@
         <v>14</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2011,16 +1958,16 @@
         <v>15</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2031,16 +1978,16 @@
         <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2051,16 +1998,16 @@
         <v>17</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2071,16 +2018,16 @@
         <v>13</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2091,16 +2038,16 @@
         <v>14</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2111,16 +2058,16 @@
         <v>15</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2131,16 +2078,16 @@
         <v>16</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2151,16 +2098,16 @@
         <v>17</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2171,16 +2118,16 @@
         <v>13</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2191,16 +2138,16 @@
         <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2211,16 +2158,16 @@
         <v>15</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2231,16 +2178,16 @@
         <v>16</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2251,16 +2198,16 @@
         <v>17</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2271,16 +2218,16 @@
         <v>13</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2291,16 +2238,16 @@
         <v>14</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2311,16 +2258,16 @@
         <v>15</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2331,16 +2278,16 @@
         <v>16</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2351,16 +2298,16 @@
         <v>17</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2371,16 +2318,16 @@
         <v>13</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2391,16 +2338,16 @@
         <v>14</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2411,16 +2358,16 @@
         <v>15</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2431,16 +2378,16 @@
         <v>16</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2451,16 +2398,16 @@
         <v>17</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2471,16 +2418,16 @@
         <v>13</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2491,16 +2438,16 @@
         <v>14</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2511,16 +2458,16 @@
         <v>15</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2531,16 +2478,16 @@
         <v>16</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2551,16 +2498,16 @@
         <v>17</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2571,16 +2518,16 @@
         <v>13</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2591,16 +2538,16 @@
         <v>14</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="F53" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2611,16 +2558,16 @@
         <v>15</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2631,16 +2578,16 @@
         <v>16</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2651,16 +2598,16 @@
         <v>17</v>
       </c>
       <c r="C56" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="F56" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2671,16 +2618,16 @@
         <v>13</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2691,16 +2638,16 @@
         <v>14</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2711,16 +2658,16 @@
         <v>15</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2731,16 +2678,16 @@
         <v>16</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2751,16 +2698,16 @@
         <v>17</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2771,16 +2718,16 @@
         <v>13</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2791,16 +2738,16 @@
         <v>14</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2811,16 +2758,16 @@
         <v>15</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2831,16 +2778,16 @@
         <v>16</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2851,16 +2798,16 @@
         <v>17</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2871,16 +2818,16 @@
         <v>13</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2891,16 +2838,16 @@
         <v>14</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2911,16 +2858,16 @@
         <v>15</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2931,16 +2878,16 @@
         <v>16</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2951,16 +2898,16 @@
         <v>17</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E71" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2971,16 +2918,16 @@
         <v>13</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2991,16 +2938,16 @@
         <v>14</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3011,16 +2958,16 @@
         <v>15</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3031,16 +2978,16 @@
         <v>16</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3051,16 +2998,16 @@
         <v>17</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3071,16 +3018,16 @@
         <v>13</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3091,16 +3038,16 @@
         <v>14</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3111,16 +3058,16 @@
         <v>15</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3131,16 +3078,16 @@
         <v>16</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3151,16 +3098,16 @@
         <v>17</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3171,16 +3118,16 @@
         <v>13</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3191,16 +3138,16 @@
         <v>14</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3211,16 +3158,16 @@
         <v>15</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3231,16 +3178,16 @@
         <v>16</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3251,16 +3198,16 @@
         <v>17</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D86" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="F86" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3271,16 +3218,16 @@
         <v>13</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3291,16 +3238,16 @@
         <v>14</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3311,16 +3258,16 @@
         <v>15</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D89" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="F89" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3331,16 +3278,16 @@
         <v>16</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D90" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F90" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3351,16 +3298,16 @@
         <v>17</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3371,16 +3318,16 @@
         <v>13</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3391,16 +3338,16 @@
         <v>14</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3411,16 +3358,16 @@
         <v>15</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3431,16 +3378,16 @@
         <v>16</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -3451,16 +3398,16 @@
         <v>17</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -3471,16 +3418,16 @@
         <v>13</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3491,16 +3438,16 @@
         <v>14</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -3511,16 +3458,16 @@
         <v>15</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3531,16 +3478,16 @@
         <v>16</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -3551,16 +3498,16 @@
         <v>17</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -3571,16 +3518,16 @@
         <v>13</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -3591,16 +3538,16 @@
         <v>14</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3611,16 +3558,16 @@
         <v>15</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -3631,16 +3578,16 @@
         <v>16</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -3651,16 +3598,16 @@
         <v>17</v>
       </c>
       <c r="C106" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="F106" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -3671,16 +3618,16 @@
         <v>13</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D107" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E107" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E107" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="F107" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -3691,16 +3638,16 @@
         <v>14</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D108" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="F108" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -3711,16 +3658,16 @@
         <v>15</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -3731,16 +3678,16 @@
         <v>16</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3751,16 +3698,16 @@
         <v>17</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -3771,16 +3718,16 @@
         <v>13</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3791,16 +3738,16 @@
         <v>14</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3811,16 +3758,16 @@
         <v>15</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -3831,16 +3778,16 @@
         <v>16</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -3851,117 +3798,32 @@
         <v>17</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A117" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B117" t="s">
-        <v>13</v>
-      </c>
-      <c r="C117" t="s">
-        <v>168</v>
-      </c>
-      <c r="D117" t="s">
-        <v>69</v>
-      </c>
-      <c r="E117" t="s">
-        <v>169</v>
-      </c>
-      <c r="F117" t="s">
-        <v>170</v>
-      </c>
+      <c r="A117" s="7"/>
     </row>
     <row r="118" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A118" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B118" t="s">
-        <v>14</v>
-      </c>
-      <c r="C118" t="s">
-        <v>171</v>
-      </c>
-      <c r="D118" t="s">
-        <v>173</v>
-      </c>
-      <c r="E118" t="s">
-        <v>171</v>
-      </c>
-      <c r="F118" t="s">
-        <v>114</v>
-      </c>
+      <c r="A118" s="7"/>
     </row>
     <row r="119" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A119" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="s">
-        <v>114</v>
-      </c>
-      <c r="D119" t="s">
-        <v>169</v>
-      </c>
-      <c r="E119" t="s">
-        <v>114</v>
-      </c>
-      <c r="F119" t="s">
-        <v>126</v>
-      </c>
+      <c r="A119" s="7"/>
     </row>
     <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A120" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B120" t="s">
-        <v>15</v>
-      </c>
-      <c r="C120" t="s">
-        <v>126</v>
-      </c>
-      <c r="D120" t="s">
-        <v>170</v>
-      </c>
-      <c r="E120" t="s">
-        <v>126</v>
-      </c>
-      <c r="F120" t="s">
-        <v>172</v>
-      </c>
+      <c r="A120" s="7"/>
     </row>
     <row r="121" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A121" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B121" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" t="s">
-        <v>172</v>
-      </c>
-      <c r="D121" t="s">
-        <v>171</v>
-      </c>
-      <c r="E121" t="s">
-        <v>172</v>
-      </c>
-      <c r="F121" t="s">
-        <v>171</v>
-      </c>
+      <c r="A121" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4004,7 +3866,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -4150,13 +4012,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -4170,7 +4032,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4335,13 +4197,13 @@
         <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -4358,7 +4220,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">

--- a/Selecciones_2026.xlsx
+++ b/Selecciones_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infog\Desktop\Golf 2027\Distinguidos_PGATour\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E77996-86CE-4EF2-B520-E44825FA5B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF22D4B-B3DC-4EC8-BB98-AF7B7C021BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="186">
   <si>
     <t>Planilla de selecciones – Distinguidos PGA Tour</t>
   </si>
@@ -526,13 +526,76 @@
   </si>
   <si>
     <t>Puntos que reciben el 1°, 2° y 3° de la polla en cada torneo. Fuente: hoja Tabla Gral. de tu Excel.</t>
+  </si>
+  <si>
+    <t>VidantaWorld Mexico Open</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Trent Phillips</t>
+  </si>
+  <si>
+    <t>Jeremy Paul</t>
+  </si>
+  <si>
+    <t>Steven Fisk</t>
+  </si>
+  <si>
+    <t>Andrew Novak</t>
+  </si>
+  <si>
+    <t>Joel Dahmen</t>
+  </si>
+  <si>
+    <t>Gordon Sargent</t>
+  </si>
+  <si>
+    <t>Trace Crowe</t>
+  </si>
+  <si>
+    <t>Brice Garnett</t>
+  </si>
+  <si>
+    <t>Austin Eckroat</t>
+  </si>
+  <si>
+    <t>Beau Hossler</t>
+  </si>
+  <si>
+    <t>Kevin Roy</t>
+  </si>
+  <si>
+    <t>Tyler Duncan</t>
+  </si>
+  <si>
+    <t>Chad Ramey</t>
+  </si>
+  <si>
+    <t>Isaiah Salinda</t>
+  </si>
+  <si>
+    <t>Cameron Tankersley</t>
+  </si>
+  <si>
+    <t>David Ford</t>
+  </si>
+  <si>
+    <t>Santiago de la Fuente</t>
+  </si>
+  <si>
+    <t>Christo Lamprecht</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -583,6 +646,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -609,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -627,6 +695,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -642,6 +711,923 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 7" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C95F2F21-4129-4B9D-BD43-D8504EF1AD85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="1645920"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 8" descr="CAN">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB47B373-B642-488D-AD9B-A4FE9094E3B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="2011680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 9" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0788A890-E62E-4B58-B13A-80C3C7A4D12C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="2377440"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 10" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2862DE21-8820-4583-93ED-AED0DC9D9EE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="2743200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 11" descr="GER">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AAF1ECD-77B9-453F-BF29-4B1FAA1E360C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="3108960"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 12" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B53E2FF2-AEFB-4141-B9B1-6AEEF731E075}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="3474720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 13" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83D08EFA-2F2C-4A9F-8B43-ED94747001AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="3840480"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 14" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5911AE25-7B36-4AD2-9898-9BEBCD70BA6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="4206240"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 15" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA9C26B-B4AB-4AFA-923A-9E62AE5E83D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="4572000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 16" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A27C6ED-FB47-4FEC-BAA7-671C1F4CD774}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="4937760"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 17" descr="CAN">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B29D3E2-E600-4260-AA71-C81ADDB89365}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="5303520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="AutoShape 18" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E48AE4-BDF8-44C8-B7B3-304F90BC6F01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="5669280"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="AutoShape 19" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{760CA0A1-34B4-4EBA-BFF1-42A80B682237}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="6035040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 20" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0865EE5-42CC-49E9-A541-24BC6F2AA678}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="6400800"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="AutoShape 21" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CECF5364-973A-49A6-8F77-38105BD97DC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="6766560"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="AutoShape 26" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DEB7642-A35F-48FD-B672-75256B6C4A1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="8595360"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="AutoShape 27" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7586AC24-78B5-4609-BBB3-BA8031E6567B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="8961120"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="AutoShape 28" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F631C3A2-ACC0-4F21-AA6E-3FD3CCBE5A51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="9326880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="AutoShape 29" descr="USA">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C452521A-59F4-44CC-BC5C-5ECCE88C03D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="9692640"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1429,12 +2415,24 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="4"/>
+      <c r="A27" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="10">
+        <v>46324</v>
+      </c>
+      <c r="D27" s="10">
+        <v>46327</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E28" s="9"/>
@@ -3811,22 +4809,108 @@
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A117" s="7"/>
+      <c r="A117" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="118" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A118" s="7"/>
+      <c r="A118" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="119" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A119" s="7"/>
+      <c r="A119" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A120" s="7"/>
+      <c r="A120" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="121" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A121" s="7"/>
+      <c r="A121" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" t="s">
+        <v>182</v>
+      </c>
+      <c r="D121" t="s">
+        <v>183</v>
+      </c>
+      <c r="E121" t="s">
+        <v>184</v>
+      </c>
+      <c r="F121" t="s">
+        <v>185</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">

--- a/Selecciones_2026.xlsx
+++ b/Selecciones_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infog\Desktop\Golf 2027\Distinguidos_PGATour\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF22D4B-B3DC-4EC8-BB98-AF7B7C021BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364686BC-882D-4FED-A2B7-A83B0E7529CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="348" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
@@ -595,6 +595,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="yyyy/mm/dd;@"/>
+  </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -677,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -694,8 +697,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2039,7 +2046,7 @@
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="3" max="4" width="14" style="13" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
   </cols>
@@ -2051,10 +2058,10 @@
       <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -2071,8 +2078,8 @@
       <c r="B2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
         <v>26</v>
@@ -2085,8 +2092,8 @@
       <c r="B3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
         <v>26</v>
@@ -2099,8 +2106,8 @@
       <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
         <v>26</v>
@@ -2113,8 +2120,8 @@
       <c r="B5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
         <v>31</v>
@@ -2127,8 +2134,8 @@
       <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
         <v>31</v>
@@ -2141,8 +2148,8 @@
       <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
         <v>31</v>
@@ -2155,8 +2162,8 @@
       <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="8"/>
       <c r="F8" s="4" t="s">
         <v>31</v>
@@ -2169,8 +2176,8 @@
       <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
       <c r="E9" s="8"/>
       <c r="F9" s="4" t="s">
         <v>36</v>
@@ -2183,8 +2190,8 @@
       <c r="B10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
       <c r="E10" s="8"/>
       <c r="F10" s="4" t="s">
         <v>36</v>
@@ -2197,8 +2204,8 @@
       <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
       <c r="E11" s="8"/>
       <c r="F11" s="4" t="s">
         <v>36</v>
@@ -2211,8 +2218,8 @@
       <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
       <c r="E12" s="8"/>
       <c r="F12" s="4" t="s">
         <v>36</v>
@@ -2225,8 +2232,8 @@
       <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="8"/>
       <c r="F13" s="4" t="s">
         <v>42</v>
@@ -2239,8 +2246,8 @@
       <c r="B14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="8"/>
       <c r="F14" s="4" t="s">
         <v>42</v>
@@ -2253,8 +2260,8 @@
       <c r="B15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="8"/>
       <c r="F15" s="4" t="s">
         <v>42</v>
@@ -2267,8 +2274,8 @@
       <c r="B16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="8"/>
       <c r="F16" s="4" t="s">
         <v>47</v>
@@ -2281,8 +2288,8 @@
       <c r="B17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
       <c r="E17" s="8"/>
       <c r="F17" s="4" t="s">
         <v>47</v>
@@ -2295,8 +2302,8 @@
       <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
       <c r="E18" s="8"/>
       <c r="F18" s="4" t="s">
         <v>47</v>
@@ -2309,8 +2316,8 @@
       <c r="B19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
       <c r="E19" s="8"/>
       <c r="F19" s="4" t="s">
         <v>47</v>
@@ -2323,8 +2330,8 @@
       <c r="B20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
       <c r="E20" s="8"/>
       <c r="F20" s="4" t="s">
         <v>47</v>
@@ -2337,8 +2344,8 @@
       <c r="B21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
       <c r="E21" s="8"/>
       <c r="F21" s="4" t="s">
         <v>53</v>
@@ -2351,8 +2358,8 @@
       <c r="B22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
       <c r="E22" s="8"/>
       <c r="F22" s="4" t="s">
         <v>53</v>
@@ -2365,8 +2372,8 @@
       <c r="B23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
       <c r="E23" s="8"/>
       <c r="F23" s="4" t="s">
         <v>53</v>
@@ -2379,8 +2386,8 @@
       <c r="B24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="4"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
       <c r="E24" s="8"/>
       <c r="F24" s="4" t="s">
         <v>53</v>
@@ -2393,8 +2400,8 @@
       <c r="B25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
       <c r="E25" s="8"/>
       <c r="F25" s="4" t="s">
         <v>58</v>
@@ -2407,8 +2414,8 @@
       <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
       <c r="E26" s="8"/>
       <c r="F26" s="4" t="s">
         <v>58</v>
@@ -2421,16 +2428,16 @@
       <c r="B27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="12">
         <v>46324</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="12">
         <v>46327</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="10" t="s">
         <v>167</v>
       </c>
     </row>

--- a/Selecciones_2026.xlsx
+++ b/Selecciones_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infog\Desktop\Golf 2027\Distinguidos_PGATour\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364686BC-882D-4FED-A2B7-A83B0E7529CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F83E0F-2A2A-404E-96D4-D450A035779F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="348" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="188">
   <si>
     <t>Planilla de selecciones – Distinguidos PGA Tour</t>
   </si>
@@ -589,6 +589,12 @@
   </si>
   <si>
     <t>Christo Lamprecht</t>
+  </si>
+  <si>
+    <t>Benjamín</t>
+  </si>
+  <si>
+    <t>Vince Whaley</t>
   </si>
 </sst>
 </file>
@@ -596,7 +602,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -698,11 +704,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1998,7 +2004,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2032,6 +2038,11 @@
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2487,7 +2498,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4915,6 +4926,26 @@
         <v>185</v>
       </c>
     </row>
+    <row r="122" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A122" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B122" t="s">
+        <v>186</v>
+      </c>
+      <c r="C122" t="s">
+        <v>187</v>
+      </c>
+      <c r="D122" t="s">
+        <v>169</v>
+      </c>
+      <c r="E122" t="s">
+        <v>173</v>
+      </c>
+      <c r="F122" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -4925,7 +4956,7 @@
           <x14:formula1>
             <xm:f>Torneos!$A$2:$A$80</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A116 A122:A500</xm:sqref>
+          <xm:sqref>A2:A116 A123:A500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0300-000001000000}">
           <x14:formula1>

--- a/Selecciones_2026.xlsx
+++ b/Selecciones_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infog\Desktop\Golf 2027\Distinguidos_PGATour\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F83E0F-2A2A-404E-96D4-D450A035779F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8259488-B3C1-49A4-93EB-C67317D85625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
